--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.7</t>
+          <t>00:010.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:020.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>148.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.7</t>
+          <t>00:030.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>153.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>230345</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.3</t>
+          <t>00:040.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>295331</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,34 +697,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.0</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>326383</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.1</t>
+          <t>00:060.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.3</t>
+          <t>01:009.9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>341890</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.1</t>
+          <t>01:020.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>135.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>465184</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.2</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>575848</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.7</t>
+          <t>01:039.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>596588</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.1</t>
+          <t>01:049.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>41307</t>
+          <t>619752</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.2</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>645553</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:009.9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>85103</t>
+          <t>671253</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>111658</t>
+          <t>692202</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1267,34 +1267,34 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.1</t>
+          <t>02:029.8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>169.9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>381.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>951961</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.6</t>
+          <t>02:040.5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>177.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>399.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>114377</t>
+          <t>1199899</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.7</t>
+          <t>02:050.1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>101146</t>
+          <t>1199083</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:055.6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>175.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>94560</t>
+          <t>1207926</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1496,6 +1496,63 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>290.8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1212927</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>

--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.2</t>
+          <t>00:020.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>148.9</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>55.13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>99472</t>
+          <t>202814</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>153.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>153.3</t>
+          <t>192.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>230345</t>
+          <t>447455</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.0</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>295331</t>
+          <t>544193</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:050.4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>326383</t>
+          <t>644500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:060.0</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>320822</t>
+          <t>704712</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.9</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>341890</t>
+          <t>731140</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.3</t>
+          <t>01:020.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>135.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>465184</t>
+          <t>812997</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.1</t>
+          <t>01:030.2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>575848</t>
+          <t>899171</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:039.8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>596588</t>
+          <t>920380</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>619752</t>
+          <t>939978</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>645553</t>
+          <t>951462</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>671253</t>
+          <t>949246</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,34 +1210,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.3</t>
+          <t>02:020.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>692202</t>
+          <t>996235</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1267,34 +1267,34 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.8</t>
+          <t>02:030.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>169.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>381.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>951961</t>
+          <t>1052551</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.5</t>
+          <t>02:039.9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>177.1</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>399.7</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1199899</t>
+          <t>1073176</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,36 +1381,36 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.1</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1199083</t>
+          <t>1072779</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.6</t>
+          <t>02:054.9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>175.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1207926</t>
+          <t>1061628</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1496,63 +1496,6 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.5</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>290.8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1212927</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
